--- a/experimental/attention/compressor_v2/tests/pytest/excel/test_cases_template.xlsx
+++ b/experimental/attention/compressor_v2/tests/pytest/excel/test_cases_template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>score_state_datarange</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>is_contiguous</t>
         </is>
       </c>
     </row>
